--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Word.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Word.xlsx
@@ -35,7 +35,7 @@
     <t xml:space="preserve">100</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.338 Patch 2</t>
+    <t xml:space="preserve">EA 23.352</t>
   </si>
   <si>
     <t xml:space="preserve">wrecked</t>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Word.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Word.xlsx
@@ -35,7 +35,7 @@
     <t xml:space="preserve">100</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.352</t>
+    <t xml:space="preserve">EA 23.355</t>
   </si>
   <si>
     <t xml:space="preserve">wrecked</t>
